--- a/slots/resources/sample/dollarexpress/dollarExpressWareHouse.xlsx
+++ b/slots/resources/sample/dollarexpress/dollarExpressWareHouse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\dollarexpress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\dollarexpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F7D963-FD9D-410B-88C9-C5A978EE656A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E4B0F2-C9DD-4A1B-9740-9B68345040F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DollarExpressWareHouse" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -246,9 +246,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -256,12 +253,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,7 +746,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="92.5" style="11" customWidth="1"/>
+    <col min="4" max="4" width="92.5" customWidth="1"/>
     <col min="5" max="5" width="13.375" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
@@ -770,7 +761,7 @@
       <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
@@ -786,10 +777,10 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
@@ -806,10 +797,10 @@
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
@@ -817,7 +808,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="6"/>
+      <c r="A4" s="2"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
@@ -831,14 +822,14 @@
       <c r="C5">
         <v>50000000</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -851,7 +842,7 @@
       <c r="C6">
         <v>500000000</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E6">
@@ -871,7 +862,7 @@
       <c r="C7">
         <v>5000000000</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E7">
